--- a/test/configs/data/develop/unit_commitment.xlsx
+++ b/test/configs/data/develop/unit_commitment.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="148">
   <si>
     <t>name</t>
   </si>
@@ -398,6 +398,78 @@
   </si>
   <si>
     <t>IT0 0 CCGT</t>
+  </si>
+  <si>
+    <t>IT0 0 H2</t>
+  </si>
+  <si>
+    <t>IT0 0 H2 Electrolysis</t>
+  </si>
+  <si>
+    <t>IT0 0 H2 Fuel Cell</t>
+  </si>
+  <si>
+    <t>IT0 1</t>
+  </si>
+  <si>
+    <t>g</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>s_nom_mod</t>
+  </si>
+  <si>
+    <t>s_nom_min</t>
+  </si>
+  <si>
+    <t>s_nom_max</t>
+  </si>
+  <si>
+    <t>s_nom_set</t>
+  </si>
+  <si>
+    <t>s_max_pu</t>
+  </si>
+  <si>
+    <t>num_parallel</t>
+  </si>
+  <si>
+    <t>v_ang_min</t>
+  </si>
+  <si>
+    <t>v_ang_max</t>
+  </si>
+  <si>
+    <t>x_pu</t>
+  </si>
+  <si>
+    <t>r_pu</t>
+  </si>
+  <si>
+    <t>g_pu</t>
+  </si>
+  <si>
+    <t>b_pu</t>
+  </si>
+  <si>
+    <t>x_pu_eff</t>
+  </si>
+  <si>
+    <t>r_pu_eff</t>
+  </si>
+  <si>
+    <t>s_nom_opt</t>
+  </si>
+  <si>
+    <t>i_nom</t>
+  </si>
+  <si>
+    <t>line 0-1</t>
+  </si>
+  <si>
+    <t>IT0 1 0 solar</t>
   </si>
 </sst>
 </file>
@@ -956,7 +1028,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:Q4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="16" bestFit="1" customWidth="1"/>
@@ -1071,23 +1143,79 @@
       </c>
     </row>
     <row r="3" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="9"/>
-      <c r="B3" s="11"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="1"/>
+      <c r="A3" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="B3" s="11">
+        <v>1</v>
+      </c>
+      <c r="D3" s="10">
+        <v>11.86</v>
+      </c>
+      <c r="E3" s="10">
+        <v>43.5</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="I3" s="11">
+        <v>1</v>
+      </c>
+      <c r="J3" s="11">
+        <v>0</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>80</v>
+      </c>
       <c r="O3" s="2"/>
-      <c r="P3" s="9"/>
+      <c r="P3" s="9" t="s">
+        <v>100</v>
+      </c>
       <c r="Q3" s="2"/>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A4" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="B4" s="17">
+        <v>380</v>
+      </c>
+      <c r="D4" s="18">
+        <v>10.1412495388794</v>
+      </c>
+      <c r="E4" s="18">
+        <v>45.348242305968</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="I4" s="17">
+        <v>1</v>
+      </c>
+      <c r="J4" s="17">
+        <v>0</v>
+      </c>
+      <c r="K4" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="L4" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="O4" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="P4" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q4" s="6" t="s">
+        <v>100</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1099,7 +1227,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="8.88671875" style="16" bestFit="1" customWidth="1"/>
@@ -1125,6 +1253,17 @@
       </c>
       <c r="C2" s="9" t="s">
         <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -1137,7 +1276,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:AJ2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="4" width="8.88671875" style="5" bestFit="1" customWidth="1"/>
@@ -1145,30 +1284,146 @@
     <col min="6" max="8" width="8.88671875" style="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="I1" t="s">
+        <v>85</v>
+      </c>
+      <c r="J1" t="s">
+        <v>130</v>
+      </c>
+      <c r="K1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L1" t="s">
+        <v>131</v>
+      </c>
+      <c r="M1" t="s">
+        <v>132</v>
+      </c>
+      <c r="N1" t="s">
+        <v>133</v>
+      </c>
+      <c r="O1" t="s">
+        <v>134</v>
+      </c>
+      <c r="P1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S1" t="s">
+        <v>25</v>
+      </c>
+      <c r="T1" t="s">
+        <v>48</v>
+      </c>
+      <c r="U1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>85</v>
+      <c r="V1" t="s">
+        <v>49</v>
+      </c>
+      <c r="W1" t="s">
+        <v>135</v>
+      </c>
+      <c r="X1" t="s">
+        <v>136</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>137</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>95</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>138</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>139</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>140</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>141</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>142</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>143</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>144</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>145</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="E2" s="5">
+        <v>5</v>
+      </c>
+      <c r="F2" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="I2">
+        <v>100</v>
+      </c>
+      <c r="K2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L2">
+        <v>100</v>
+      </c>
+      <c r="M2">
+        <v>10000</v>
+      </c>
+      <c r="P2">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1181,7 +1436,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:AM2"/>
+  <dimension ref="A1:AM3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.109375" style="5" bestFit="1" customWidth="1"/>
@@ -1341,7 +1596,7 @@
       </c>
       <c r="D2"/>
       <c r="E2">
-        <v>10000</v>
+        <v>500</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -1417,13 +1672,13 @@
         <v>2</v>
       </c>
       <c r="AD2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG2">
         <v>0.5</v>
@@ -1444,6 +1699,120 @@
         <v>39535.519999999997</v>
       </c>
       <c r="AM2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D3"/>
+      <c r="E3">
+        <v>1000</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3">
+        <v>19711.869183731302</v>
+      </c>
+      <c r="I3">
+        <v>725545.55299179</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3" t="e">
+        <f t="shared" ref="M3" si="1">-inf</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="N3" t="s">
+        <v>31</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>81</v>
+      </c>
+      <c r="R3">
+        <v>0.01</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>35</v>
+      </c>
+      <c r="W3">
+        <v>54744.164802564301</v>
+      </c>
+      <c r="X3">
+        <v>1</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>1</v>
+      </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3"/>
+      <c r="AH3"/>
+      <c r="AI3">
+        <v>1</v>
+      </c>
+      <c r="AJ3">
+        <v>1</v>
+      </c>
+      <c r="AK3">
+        <v>1</v>
+      </c>
+      <c r="AL3">
+        <v>62875.819329802704</v>
+      </c>
+      <c r="AM3">
         <v>0</v>
       </c>
     </row>
@@ -1624,98 +1993,222 @@
       </c>
     </row>
     <row r="2" spans="1:45" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="12"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="2"/>
-      <c r="T2" s="2"/>
-      <c r="U2" s="2"/>
-      <c r="V2" s="2"/>
-      <c r="W2" s="2"/>
-      <c r="X2" s="1"/>
-      <c r="Y2" s="2"/>
-      <c r="Z2" s="2"/>
-      <c r="AA2" s="2"/>
-      <c r="AB2" s="2"/>
-      <c r="AC2" s="2"/>
-      <c r="AD2" s="2"/>
-      <c r="AE2" s="1"/>
-      <c r="AF2" s="1"/>
-      <c r="AG2" s="2"/>
-      <c r="AH2" s="2"/>
-      <c r="AI2" s="2"/>
-      <c r="AJ2" s="1"/>
-      <c r="AK2" s="1"/>
+      <c r="A2" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F2" s="4">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H2" s="2">
+        <v>0</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" s="2">
+        <v>100</v>
+      </c>
+      <c r="K2" s="2">
+        <v>0</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="M2" s="2">
+        <v>0</v>
+      </c>
+      <c r="N2" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="O2" s="2">
+        <v>0</v>
+      </c>
+      <c r="P2" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>1</v>
+      </c>
+      <c r="R2" s="4">
+        <v>251621.03</v>
+      </c>
+      <c r="S2" s="2">
+        <v>0</v>
+      </c>
+      <c r="T2" s="2">
+        <v>0</v>
+      </c>
+      <c r="U2" s="2">
+        <v>0</v>
+      </c>
+      <c r="V2" s="2">
+        <v>0</v>
+      </c>
+      <c r="W2" s="2">
+        <v>1</v>
+      </c>
+      <c r="X2" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y2" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="2">
+        <v>1</v>
+      </c>
+      <c r="AD2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG2" s="2">
+        <v>1</v>
+      </c>
+      <c r="AH2" s="2">
+        <v>1</v>
+      </c>
+      <c r="AI2" s="2">
+        <v>0</v>
+      </c>
       <c r="AL2" s="2"/>
-      <c r="AM2" s="1"/>
       <c r="AN2" s="2"/>
       <c r="AO2" s="2"/>
       <c r="AP2" s="2"/>
       <c r="AQ2" s="4"/>
-      <c r="AR2" s="2"/>
-      <c r="AS2" s="2"/>
+      <c r="AR2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AS2" s="2">
+        <v>2</v>
+      </c>
     </row>
     <row r="3" spans="1:45" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="12"/>
-      <c r="O3" s="2"/>
-      <c r="P3" s="2"/>
-      <c r="Q3" s="2"/>
-      <c r="R3" s="4"/>
-      <c r="S3" s="2"/>
-      <c r="T3" s="2"/>
-      <c r="U3" s="2"/>
-      <c r="V3" s="2"/>
-      <c r="W3" s="2"/>
-      <c r="X3" s="1"/>
-      <c r="Y3" s="2"/>
-      <c r="Z3" s="2"/>
-      <c r="AA3" s="2"/>
-      <c r="AB3" s="2"/>
-      <c r="AC3" s="2"/>
-      <c r="AD3" s="2"/>
-      <c r="AE3" s="1"/>
-      <c r="AF3" s="1"/>
-      <c r="AG3" s="2"/>
-      <c r="AH3" s="2"/>
-      <c r="AI3" s="2"/>
-      <c r="AJ3" s="1"/>
-      <c r="AK3" s="1"/>
+      <c r="A3" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F3" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" s="2">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" s="2">
+        <v>100</v>
+      </c>
+      <c r="K3" s="2">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="M3" s="2">
+        <v>0</v>
+      </c>
+      <c r="N3" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="O3" s="2">
+        <v>0</v>
+      </c>
+      <c r="P3" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>1</v>
+      </c>
+      <c r="R3" s="4">
+        <v>132325.72</v>
+      </c>
+      <c r="S3" s="2">
+        <v>0</v>
+      </c>
+      <c r="T3" s="2">
+        <v>0</v>
+      </c>
+      <c r="U3" s="2">
+        <v>0</v>
+      </c>
+      <c r="V3" s="2">
+        <v>0</v>
+      </c>
+      <c r="W3" s="2">
+        <v>1</v>
+      </c>
+      <c r="X3" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y3" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="2">
+        <v>1</v>
+      </c>
+      <c r="AD3" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="2">
+        <v>1</v>
+      </c>
+      <c r="AH3" s="2">
+        <v>1</v>
+      </c>
+      <c r="AI3" s="2">
+        <v>0</v>
+      </c>
       <c r="AL3" s="2"/>
-      <c r="AM3" s="1"/>
       <c r="AN3" s="2"/>
       <c r="AO3" s="2"/>
       <c r="AP3" s="2"/>
       <c r="AQ3" s="4"/>
-      <c r="AR3" s="2"/>
-      <c r="AS3" s="2"/>
+      <c r="AR3" s="2">
+        <v>2</v>
+      </c>
+      <c r="AS3" s="2">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1901,35 +2394,88 @@
       </c>
     </row>
     <row r="2" spans="1:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="2"/>
+      <c r="A2" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="2">
+        <v>100</v>
+      </c>
       <c r="F2" s="2"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
-      <c r="S2" s="2"/>
-      <c r="T2" s="2"/>
-      <c r="U2" s="2"/>
-      <c r="V2" s="4"/>
-      <c r="W2" s="2"/>
-      <c r="X2" s="1"/>
-      <c r="Y2" s="2"/>
-      <c r="Z2" s="1"/>
-      <c r="AA2" s="2"/>
-      <c r="AB2" s="2"/>
-      <c r="AC2" s="2"/>
+      <c r="G2" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2" s="2">
+        <v>0</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" s="2">
+        <v>0</v>
+      </c>
+      <c r="K2" s="2">
+        <v>1</v>
+      </c>
+      <c r="L2" s="2">
+        <v>0</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="P2" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>0</v>
+      </c>
+      <c r="R2" s="2">
+        <v>1</v>
+      </c>
+      <c r="S2" s="2">
+        <v>0</v>
+      </c>
+      <c r="T2" s="2">
+        <v>0</v>
+      </c>
+      <c r="U2" s="2">
+        <v>0</v>
+      </c>
+      <c r="V2" s="4">
+        <v>222.49</v>
+      </c>
+      <c r="W2" s="2">
+        <v>0</v>
+      </c>
+      <c r="X2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y2" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="AA2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="2">
+        <v>10</v>
+      </c>
+      <c r="AC2" s="2">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
